--- a/introduction.xlsx
+++ b/introduction.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wenteliao/Desktop/系網部署包_2026-07-06b/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wenteliao/SynologyDrive/00PhysWeb_v3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2011B619-EEA7-5748-91AA-BDAE59A099AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA00CA18-3EFD-A447-9755-EC8A449495C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="160" yWindow="920" windowWidth="29080" windowHeight="16740" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3717,7 +3717,7 @@
         <v>682</v>
       </c>
       <c r="E8" t="s">
-        <v>279</v>
+        <v>298</v>
       </c>
       <c r="F8" t="s">
         <v>291</v>
